--- a/02_加值成品/八上/八上4-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上4-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上4-2 光的折射與透鏡　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上4-2 光的折射與透鏡　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>光過介質界面方向改變稱？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>偏向法線</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>變慢</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>折射</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>方向變</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>光由空氣進水偏向或偏離法線？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>凸透鏡</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>凹透鏡</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>偏向法線</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>倒立放大實像</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>進密介質</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>中間厚會聚光的透鏡是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>凸透鏡</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>正立縮小虛像</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>倒立放大實像</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>凹透鏡</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>會聚</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>中間薄發散光的透鏡是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>偏離法線</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>正立縮小虛像</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>凹透鏡</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>發散</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>放大鏡是哪種透鏡？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>偏向法線</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>倒立放大實像</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>凸透鏡</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>放大虛像</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>近視眼鏡用哪種透鏡？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>倒立放大實像</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>凹透鏡</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>倒立</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>厚</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>發散</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>光垂直入射界面會偏折嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>偏向法線</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>偏離法線</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>不會</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>凸透鏡</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>沿原方向</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>水中筷子看似折斷因為？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>正立縮小虛像</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>變慢</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>折射</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>界面</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>光進入另一介質速度改變會？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>倒立縮小實像</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>凹透鏡</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>折射</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>厚</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>折射</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>凸透鏡中央比邊緣？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>倒立縮小實像</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>大於臨界角</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>偏離法線</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>厚</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>會聚</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上4-2 光的折射與透鏡　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上4-2 光的折射與透鏡　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>光由水進空氣偏向或偏離法線？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>厚</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>偏離法線</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>凸透鏡</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>凹透鏡</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>進疏介質</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>凸透鏡物在兩倍焦距外成？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>凹透鏡</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>折射</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>倒立縮小實像</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>照相機</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>凸透鏡物在焦距內成？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>變慢</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>正立放大虛像</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>倒立</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>偏離法線</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>放大鏡</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>凹透鏡成什麼像？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>大於臨界角</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>正立縮小虛像</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>倒立放大實像</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>恆虛</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>遠視眼鏡用哪種透鏡？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>正立放大虛像</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>厚</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>正立縮小虛像</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>凸透鏡</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>會聚補足</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>光斜射入玻璃，速度如何變？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>變慢</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>倒立縮小實像</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>折射</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>密介質</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>凸透鏡物在焦點上成？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>由小變大、超焦點內轉虛像</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>不成像(平行射出)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>水中光折射使像位置偏移</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>凹透鏡發散使像後移</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>特殊</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>池水看起來比實際淺因為？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>偏向法線</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>大於臨界角</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>真空</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>折射</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>視深變淺</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>凸透鏡物在一倍與兩倍焦距間成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>偏向法線</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>大於臨界角</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>倒立放大實像</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>厚</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>投影</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>光垂直射入界面是否折射？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>正立放大虛像</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>折射</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>不折射</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>凸透鏡</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>沿原方向</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上4-2 光的折射與透鏡　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上4-2 光的折射與透鏡　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何插入水中的筷子看似彎折？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>由小變大、超焦點內轉虛像</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>水中光折射使像位置偏移</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>不成像(平行射出)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>凹透鏡發散使像後移</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>折射成像</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>凸透鏡成實像時像的正倒？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>偏向法線</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>不折射</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>變慢</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>倒立</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>實像特性</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>近視眼球太長，像成在視網膜前，用？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>凹透鏡發散使像後移</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>由小變大、超焦點內轉虛像</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>水中光折射使像位置偏移</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>不成像(平行射出)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>矯正原理</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>凸透鏡物由遠移近像如何變？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>不成像(平行射出)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>凹透鏡發散使像後移</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>由小變大、超焦點內轉虛像</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>水中光折射使像位置偏移</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>成像規律</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>光速在真空與水中何者快？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>真空</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>大於臨界角</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>凸透鏡</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>折射</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>密介質變慢</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>全反射發生在光由密到疏且角度？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>折射</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>正立放大虛像</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>凹透鏡</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>大於臨界角</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>全反射</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>照相機用凸透鏡成何像？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>倒立</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>倒立縮小實像</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>偏離法線</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>底片</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>凹透鏡能當放大鏡嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>變慢</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>倒立</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>折射</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>只成縮小像</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>放大鏡看報紙字變大是何成像？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>正立放大虛像</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>正立縮小虛像</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>折射</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>凸透鏡</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>焦距內</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>海市蜃樓與光的什麼現象有關？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>折射</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>凹透鏡</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>凸透鏡</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>倒立</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>折射</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上4-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上4-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>方向變</t>
+          <t>方向變：光從一種介質進入另一種介質時，因為傳播速度改變，行進方向會偏折，這個現象稱為折射</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>進密介質</t>
+          <t>進密介質：光從較稀疏的空氣進入較緻密的水中，速度變慢，會偏向法線</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>會聚</t>
+          <t>會聚：凸透鏡中央比邊緣厚，能把平行光線往中間聚集，具有會聚光線的效果</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>發散</t>
+          <t>發散：凹透鏡中央比邊緣薄，會把平行光線向外分散開來，具有發散光線的效果</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>放大虛像</t>
+          <t>放大虛像：放大鏡是凸透鏡，把物體放在焦距以內時能成正立放大的虛像</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>發散</t>
+          <t>發散：近視是因為影像成在視網膜前方，需要用能讓光線提早發散的凹透鏡矯正，把焦點往後移到視網膜上</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>沿原方向</t>
+          <t>沿原方向：光線垂直射入兩介質的交界面時，入射角是0度，不會發生偏折，仍沿原來的方向前進</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>界面</t>
+          <t>界面：筷子在水面下的部分，反射的光線經過水和空氣的交界面時發生折射，改變方向後進入眼睛，讓筷子看起來像是斷掉了</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>折射</t>
+          <t>折射：光從一種介質進入另一種介質時，因為傳播速度改變，行進方向會偏折，這個現象稱為折射</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>會聚</t>
+          <t>會聚：凸透鏡中央比邊緣厚，能把平行光線往中間聚集，具有會聚光線的效果</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>進疏介質</t>
+          <t>進疏介質：光從較緻密的水進入較稀疏的空氣，速度變快，會偏離法線</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>照相機</t>
+          <t>照相機：把物體放在凸透鏡兩倍焦距以外時，會成一個顛倒、縮小的實像，這正是照相機成像的原理</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>放大鏡</t>
+          <t>放大鏡：把物體放在凸透鏡焦距以內時，會成一個正立、放大的虛像，這正是放大鏡的成像原理</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>恆虛</t>
+          <t>恆虛：凹透鏡不論物體放在哪裡，永遠只會成正立、縮小的虛像，不會成實像</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>會聚補足</t>
+          <t>會聚補足：遠視是因為影像成在視網膜後方，需要用能讓光線提早會聚的凸透鏡矯正，把焦點往前移到視網膜上</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>密介質</t>
+          <t>密介質：玻璃是比空氣更緻密的介質，光進入玻璃後傳播速度會變慢，也因此發生折射</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>特殊</t>
+          <t>特殊：把物體放在凸透鏡的焦點上時，通過透鏡的光線會變成互相平行射出，不會在任何位置交會，所以不成像</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>視深變淺</t>
+          <t>視深變淺：水底反射的光線經過水面折射後才進入眼睛，這個折射效果使我們判斷的池水深度比實際深度來得淺</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>投影</t>
+          <t>投影：當物體放在凸透鏡的一倍焦距和兩倍焦距之間時，會成一個顛倒、放大的實像，這是投影機成像的原理</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>沿原方向</t>
+          <t>沿原方向：光線垂直射入兩介質的交界面時，入射角是0度，不會發生偏折，仍沿原來的方向前進</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>折射成像</t>
+          <t>折射成像：水中筷子部分反射的光線經過水面時發生折射，改變了光線方向，使眼睛判斷出來的位置和實際位置有偏移，看起來就像在水面處彎折了</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>實像特性</t>
+          <t>實像特性：凸透鏡成實像時，光線是真正交會而成的，成像過程中光線上下左右交叉，所以實像一定是倒立的</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>矯正原理</t>
+          <t>矯正原理：近視眼球前後太長，使影像提早在視網膜前方聚焦，戴凹透鏡讓光線先發散一些，可以把焦點往後推移到剛好落在視網膜上</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>成像規律</t>
+          <t>成像規律：物體從遠處慢慢移近凸透鏡時，成的實像會逐漸變大，一旦移到焦點以內，就會改成正立放大的虛像</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>密介質變慢</t>
+          <t>密介質變慢：真空中沒有介質阻礙，光速最快；水是比真空緻密的介質，光在水中傳播速度會變慢</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>全反射</t>
+          <t>全反射：光從較緻密介質進入較稀疏介質，當入射角大於某個特定角度(臨界角)時，光不會折射穿出，而是完全反射回原介質，這種現象稱為全反射</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>底片</t>
+          <t>底片：照相機的鏡頭是凸透鏡，把遠處的景物成一個顛倒、縮小的實像投影在底片(或感光元件)上</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>只成縮小像</t>
+          <t>只成縮小像：凹透鏡不論物體放在哪個位置，永遠只會成正立縮小的虛像，不會把物體放大，所以不能當放大鏡使用</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>焦距內</t>
+          <t>焦距內：把凸透鏡(放大鏡)放在物體(字)的一倍焦距以內時，會成一個正立、放大的虛像，這就是放大鏡的成像原理</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>折射</t>
+          <t>折射：海市蜃樓是因為不同溫度的空氣密度不同，光線通過時連續發生折射彎曲，讓遠方景物的影像出現在不該出現的位置</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上4-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上4-2_三種難度測驗卷.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>不會</t>
+          <t>倒立縮小實像</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>厚</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>偏向法線</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>變慢</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>不會</t>
+          <t>偏向法線</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>正立縮小虛像</t>
+          <t>凹透鏡</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>變慢</t>
+          <t>倒立放大實像</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>倒立縮小實像</t>
+          <t>真空</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>凹透鏡</t>
+          <t>偏離法線</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>厚</t>
+          <t>大於臨界角</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1079,17 +1079,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
+          <t>凸透鏡</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
           <t>不會</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>凹透鏡</t>
-        </is>
-      </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>折射</t>
+          <t>倒立放大實像</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>偏向法線</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>大於臨界角</t>
+          <t>凹透鏡</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>偏向法線</t>
+          <t>折射</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>大於臨界角</t>
+          <t>正立放大虛像</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>厚</t>
+          <t>不會</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>正立放大虛像</t>
+          <t>凹透鏡</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>折射</t>
+          <t>凸透鏡</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>凸透鏡</t>
+          <t>不會</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>偏向法線</t>
+          <t>凸透鏡</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>不折射</t>
+          <t>厚</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>變慢</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>倒立</t>
+          <t>凹透鏡</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>不會</t>
+          <t>偏向法線</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>偏離法線</t>
+          <t>倒立放大實像</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1880,17 +1880,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>凹透鏡</t>
+          <t>不會</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>凸透鏡</t>
+          <t>倒立放大實像</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>倒立</t>
+          <t>正立放大虛像</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
